--- a/assets/resume/IMI Optimization Solution Matrix Worksheet (Blank).xlsx
+++ b/assets/resume/IMI Optimization Solution Matrix Worksheet (Blank).xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\4cata\Documents\catalina-garcia.com\assets\resume\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7409B384-DBCC-4871-84C0-32C9C4D25E8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61AE902C-32D3-4C61-BBA9-84429690A3E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="135" windowWidth="38640" windowHeight="15720" xr2:uid="{3171F72F-7B31-4104-B342-27A2432771E9}"/>
   </bookViews>
@@ -284,7 +284,7 @@
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -340,16 +340,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="16">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -389,12 +381,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14999847407452621"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -700,7 +686,7 @@
     <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -734,116 +720,112 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="0" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="7" fillId="8" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="4" fillId="14" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="4" fillId="13" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="14" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="14" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="13" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="14" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="4" fillId="14" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="14" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="14" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="14" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="4" fillId="14" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="14" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="14" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="13" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="13" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="13" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="4" fillId="15" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="15" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="15" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="15" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="4" fillId="13" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="1" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="44" fontId="4" fillId="13" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="13" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -851,7 +833,44 @@
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="8">
+  <dxfs count="17">
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -931,6 +950,78 @@
       <fill>
         <patternFill>
           <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1862,37 +1953,37 @@
     <row r="2" spans="2:28" x14ac:dyDescent="0.25">
       <c r="W2" s="4"/>
       <c r="X2" s="4"/>
-      <c r="Y2" s="31"/>
-      <c r="Z2" s="31"/>
+      <c r="Y2" s="29"/>
+      <c r="Z2" s="29"/>
     </row>
     <row r="3" spans="2:28" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="C3" s="40" t="s">
+      <c r="C3" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="40"/>
-      <c r="E3" s="40"/>
-      <c r="F3" s="40"/>
-      <c r="G3" s="40"/>
-      <c r="H3" s="40"/>
-      <c r="I3" s="40"/>
-      <c r="J3" s="40"/>
-      <c r="K3" s="40"/>
-      <c r="L3" s="40"/>
-      <c r="M3" s="40"/>
-      <c r="N3" s="40"/>
-      <c r="O3" s="40"/>
-      <c r="P3" s="40"/>
-      <c r="Q3" s="40"/>
-      <c r="R3" s="40"/>
-      <c r="S3" s="40"/>
-      <c r="T3" s="40"/>
-      <c r="U3" s="40"/>
-      <c r="W3" s="40" t="s">
+      <c r="D3" s="41"/>
+      <c r="E3" s="41"/>
+      <c r="F3" s="41"/>
+      <c r="G3" s="41"/>
+      <c r="H3" s="41"/>
+      <c r="I3" s="41"/>
+      <c r="J3" s="41"/>
+      <c r="K3" s="41"/>
+      <c r="L3" s="41"/>
+      <c r="M3" s="41"/>
+      <c r="N3" s="41"/>
+      <c r="O3" s="41"/>
+      <c r="P3" s="41"/>
+      <c r="Q3" s="41"/>
+      <c r="R3" s="41"/>
+      <c r="S3" s="41"/>
+      <c r="T3" s="41"/>
+      <c r="U3" s="41"/>
+      <c r="W3" s="41" t="s">
         <v>2</v>
       </c>
-      <c r="X3" s="40"/>
-      <c r="Y3" s="40"/>
-      <c r="Z3" s="40"/>
+      <c r="X3" s="41"/>
+      <c r="Y3" s="41"/>
+      <c r="Z3" s="41"/>
     </row>
     <row r="4" spans="2:28" x14ac:dyDescent="0.25">
       <c r="D4" s="5">
@@ -2045,8 +2136,8 @@
       <c r="U6" s="11"/>
       <c r="W6" s="4"/>
       <c r="X6" s="4"/>
-      <c r="Y6" s="31"/>
-      <c r="Z6" s="31"/>
+      <c r="Y6" s="29"/>
+      <c r="Z6" s="29"/>
     </row>
     <row r="7" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B7" s="12" t="s">
@@ -2061,31 +2152,31 @@
       <c r="G7" s="14"/>
       <c r="H7" s="14"/>
       <c r="I7" s="14"/>
-      <c r="J7" s="15"/>
+      <c r="J7" s="14"/>
       <c r="K7" s="14"/>
-      <c r="L7" s="15"/>
+      <c r="L7" s="14"/>
       <c r="M7" s="14"/>
       <c r="N7" s="14"/>
-      <c r="O7" s="15"/>
-      <c r="P7" s="15"/>
+      <c r="O7" s="14"/>
+      <c r="P7" s="14"/>
       <c r="Q7" s="14"/>
-      <c r="R7" s="15"/>
+      <c r="R7" s="14"/>
       <c r="S7" s="14"/>
       <c r="T7" s="14"/>
       <c r="U7" s="14"/>
-      <c r="W7" s="41" t="s">
+      <c r="W7" s="39" t="s">
         <v>29</v>
       </c>
-      <c r="X7" s="42">
+      <c r="X7" s="40">
         <f>W26+W27</f>
         <v>0</v>
       </c>
-      <c r="Y7" s="42"/>
-      <c r="Z7" s="42"/>
-      <c r="AA7" s="16" t="s">
+      <c r="Y7" s="40"/>
+      <c r="Z7" s="40"/>
+      <c r="AA7" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="AB7" s="17" t="b">
+      <c r="AB7" s="16" t="b">
         <f>IF(X7&gt;=Y7,TRUE,FALSE)</f>
         <v>1</v>
       </c>
@@ -2103,26 +2194,26 @@
       <c r="G8" s="14"/>
       <c r="H8" s="14"/>
       <c r="I8" s="14"/>
-      <c r="J8" s="15"/>
+      <c r="J8" s="14"/>
       <c r="K8" s="14"/>
-      <c r="L8" s="15"/>
+      <c r="L8" s="14"/>
       <c r="M8" s="14"/>
       <c r="N8" s="14"/>
-      <c r="O8" s="15"/>
-      <c r="P8" s="15"/>
+      <c r="O8" s="14"/>
+      <c r="P8" s="14"/>
       <c r="Q8" s="14"/>
-      <c r="R8" s="15"/>
+      <c r="R8" s="14"/>
       <c r="S8" s="14"/>
       <c r="T8" s="14"/>
       <c r="U8" s="14"/>
-      <c r="W8" s="41"/>
-      <c r="X8" s="42"/>
-      <c r="Y8" s="42"/>
-      <c r="Z8" s="42"/>
-      <c r="AA8" s="16" t="s">
+      <c r="W8" s="39"/>
+      <c r="X8" s="40"/>
+      <c r="Y8" s="40"/>
+      <c r="Z8" s="40"/>
+      <c r="AA8" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="AB8" s="17" t="b">
+      <c r="AB8" s="16" t="b">
         <f>IF(X7&lt;=Z7,TRUE,FALSE)</f>
         <v>1</v>
       </c>
@@ -2151,20 +2242,20 @@
       <c r="R9" s="14"/>
       <c r="S9" s="14"/>
       <c r="T9" s="14"/>
-      <c r="U9" s="15"/>
-      <c r="W9" s="41" t="s">
+      <c r="U9" s="14"/>
+      <c r="W9" s="39" t="s">
         <v>35</v>
       </c>
-      <c r="X9" s="42">
+      <c r="X9" s="40">
         <f>W28+W29</f>
         <v>0</v>
       </c>
-      <c r="Y9" s="42"/>
-      <c r="Z9" s="42"/>
-      <c r="AA9" s="16" t="s">
+      <c r="Y9" s="40"/>
+      <c r="Z9" s="40"/>
+      <c r="AA9" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="AB9" s="17" t="b">
+      <c r="AB9" s="16" t="b">
         <f t="shared" ref="AB9" si="0">IF(X9&gt;=Y9,TRUE,FALSE)</f>
         <v>1</v>
       </c>
@@ -2193,15 +2284,15 @@
       <c r="R10" s="14"/>
       <c r="S10" s="14"/>
       <c r="T10" s="14"/>
-      <c r="U10" s="15"/>
-      <c r="W10" s="41"/>
-      <c r="X10" s="42"/>
-      <c r="Y10" s="42"/>
-      <c r="Z10" s="42"/>
-      <c r="AA10" s="16" t="s">
+      <c r="U10" s="14"/>
+      <c r="W10" s="39"/>
+      <c r="X10" s="40"/>
+      <c r="Y10" s="40"/>
+      <c r="Z10" s="40"/>
+      <c r="AA10" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="AB10" s="17" t="b">
+      <c r="AB10" s="16" t="b">
         <f t="shared" ref="AB10" si="1">IF(X9&lt;=Z9,TRUE,FALSE)</f>
         <v>1</v>
       </c>
@@ -2230,20 +2321,20 @@
       <c r="R11" s="14"/>
       <c r="S11" s="14"/>
       <c r="T11" s="14"/>
-      <c r="U11" s="15"/>
-      <c r="W11" s="41" t="s">
+      <c r="U11" s="14"/>
+      <c r="W11" s="39" t="s">
         <v>40</v>
       </c>
-      <c r="X11" s="42">
+      <c r="X11" s="40">
         <f>W30+W31</f>
         <v>0</v>
       </c>
-      <c r="Y11" s="42"/>
-      <c r="Z11" s="42"/>
-      <c r="AA11" s="16" t="s">
+      <c r="Y11" s="40"/>
+      <c r="Z11" s="40"/>
+      <c r="AA11" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="AB11" s="17" t="b">
+      <c r="AB11" s="16" t="b">
         <f t="shared" ref="AB11" si="2">IF(X11&gt;=Y11,TRUE,FALSE)</f>
         <v>1</v>
       </c>
@@ -2272,15 +2363,15 @@
       <c r="R12" s="14"/>
       <c r="S12" s="14"/>
       <c r="T12" s="14"/>
-      <c r="U12" s="15"/>
-      <c r="W12" s="41"/>
-      <c r="X12" s="42"/>
-      <c r="Y12" s="42"/>
-      <c r="Z12" s="42"/>
-      <c r="AA12" s="16" t="s">
+      <c r="U12" s="14"/>
+      <c r="W12" s="39"/>
+      <c r="X12" s="40"/>
+      <c r="Y12" s="40"/>
+      <c r="Z12" s="40"/>
+      <c r="AA12" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="AB12" s="17" t="b">
+      <c r="AB12" s="16" t="b">
         <f t="shared" ref="AB12" si="3">IF(X11&lt;=Z11,TRUE,FALSE)</f>
         <v>1</v>
       </c>
@@ -2292,37 +2383,37 @@
       <c r="C13" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="D13" s="15"/>
-      <c r="E13" s="15"/>
-      <c r="F13" s="15"/>
+      <c r="D13" s="14"/>
+      <c r="E13" s="14"/>
+      <c r="F13" s="14"/>
       <c r="G13" s="14"/>
-      <c r="H13" s="15"/>
-      <c r="I13" s="15"/>
-      <c r="J13" s="15"/>
-      <c r="K13" s="15"/>
-      <c r="L13" s="15"/>
-      <c r="M13" s="15"/>
-      <c r="N13" s="15"/>
+      <c r="H13" s="14"/>
+      <c r="I13" s="14"/>
+      <c r="J13" s="14"/>
+      <c r="K13" s="14"/>
+      <c r="L13" s="14"/>
+      <c r="M13" s="14"/>
+      <c r="N13" s="14"/>
       <c r="O13" s="14"/>
-      <c r="P13" s="15"/>
-      <c r="Q13" s="15"/>
-      <c r="R13" s="15"/>
+      <c r="P13" s="14"/>
+      <c r="Q13" s="14"/>
+      <c r="R13" s="14"/>
       <c r="S13" s="14"/>
-      <c r="T13" s="15"/>
-      <c r="U13" s="15"/>
-      <c r="W13" s="41" t="s">
+      <c r="T13" s="14"/>
+      <c r="U13" s="14"/>
+      <c r="W13" s="39" t="s">
         <v>45</v>
       </c>
-      <c r="X13" s="42">
+      <c r="X13" s="40">
         <f>W32+W33</f>
         <v>0</v>
       </c>
-      <c r="Y13" s="42"/>
-      <c r="Z13" s="42"/>
-      <c r="AA13" s="16" t="s">
+      <c r="Y13" s="40"/>
+      <c r="Z13" s="40"/>
+      <c r="AA13" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="AB13" s="17" t="b">
+      <c r="AB13" s="16" t="b">
         <f t="shared" ref="AB13" si="4">IF(X13&gt;=Y13,TRUE,FALSE)</f>
         <v>1</v>
       </c>
@@ -2334,32 +2425,32 @@
       <c r="C14" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="D14" s="15"/>
-      <c r="E14" s="15"/>
-      <c r="F14" s="15"/>
+      <c r="D14" s="14"/>
+      <c r="E14" s="14"/>
+      <c r="F14" s="14"/>
       <c r="G14" s="14"/>
-      <c r="H14" s="15"/>
-      <c r="I14" s="15"/>
-      <c r="J14" s="15"/>
-      <c r="K14" s="15"/>
-      <c r="L14" s="15"/>
-      <c r="M14" s="15"/>
-      <c r="N14" s="15"/>
+      <c r="H14" s="14"/>
+      <c r="I14" s="14"/>
+      <c r="J14" s="14"/>
+      <c r="K14" s="14"/>
+      <c r="L14" s="14"/>
+      <c r="M14" s="14"/>
+      <c r="N14" s="14"/>
       <c r="O14" s="14"/>
-      <c r="P14" s="15"/>
-      <c r="Q14" s="15"/>
-      <c r="R14" s="15"/>
+      <c r="P14" s="14"/>
+      <c r="Q14" s="14"/>
+      <c r="R14" s="14"/>
       <c r="S14" s="14"/>
-      <c r="T14" s="15"/>
-      <c r="U14" s="15"/>
-      <c r="W14" s="41"/>
-      <c r="X14" s="42"/>
-      <c r="Y14" s="42"/>
-      <c r="Z14" s="42"/>
-      <c r="AA14" s="16" t="s">
+      <c r="T14" s="14"/>
+      <c r="U14" s="14"/>
+      <c r="W14" s="39"/>
+      <c r="X14" s="40"/>
+      <c r="Y14" s="40"/>
+      <c r="Z14" s="40"/>
+      <c r="AA14" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="AB14" s="17" t="b">
+      <c r="AB14" s="16" t="b">
         <f t="shared" ref="AB14" si="5">IF(X13&lt;=Z13,TRUE,FALSE)</f>
         <v>1</v>
       </c>
@@ -2371,37 +2462,37 @@
       <c r="C15" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="D15" s="15"/>
-      <c r="E15" s="15"/>
-      <c r="F15" s="15"/>
+      <c r="D15" s="14"/>
+      <c r="E15" s="14"/>
+      <c r="F15" s="14"/>
       <c r="G15" s="14"/>
-      <c r="H15" s="15"/>
-      <c r="I15" s="15"/>
-      <c r="J15" s="15"/>
+      <c r="H15" s="14"/>
+      <c r="I15" s="14"/>
+      <c r="J15" s="14"/>
       <c r="K15" s="14"/>
       <c r="L15" s="14"/>
-      <c r="M15" s="15"/>
-      <c r="N15" s="15"/>
+      <c r="M15" s="14"/>
+      <c r="N15" s="14"/>
       <c r="O15" s="14"/>
-      <c r="P15" s="15"/>
-      <c r="Q15" s="15"/>
-      <c r="R15" s="15"/>
+      <c r="P15" s="14"/>
+      <c r="Q15" s="14"/>
+      <c r="R15" s="14"/>
       <c r="S15" s="14"/>
-      <c r="T15" s="15"/>
-      <c r="U15" s="15"/>
-      <c r="W15" s="41" t="s">
+      <c r="T15" s="14"/>
+      <c r="U15" s="14"/>
+      <c r="W15" s="39" t="s">
         <v>50</v>
       </c>
-      <c r="X15" s="42">
+      <c r="X15" s="40">
         <f>W34+W35</f>
         <v>0</v>
       </c>
-      <c r="Y15" s="42"/>
-      <c r="Z15" s="42"/>
-      <c r="AA15" s="16" t="s">
+      <c r="Y15" s="40"/>
+      <c r="Z15" s="40"/>
+      <c r="AA15" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="AB15" s="17" t="b">
+      <c r="AB15" s="16" t="b">
         <f t="shared" ref="AB15" si="6">IF(X15&gt;=Y15,TRUE,FALSE)</f>
         <v>1</v>
       </c>
@@ -2413,32 +2504,32 @@
       <c r="C16" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="D16" s="15"/>
-      <c r="E16" s="15"/>
-      <c r="F16" s="15"/>
+      <c r="D16" s="14"/>
+      <c r="E16" s="14"/>
+      <c r="F16" s="14"/>
       <c r="G16" s="14"/>
-      <c r="H16" s="15"/>
-      <c r="I16" s="15"/>
-      <c r="J16" s="15"/>
+      <c r="H16" s="14"/>
+      <c r="I16" s="14"/>
+      <c r="J16" s="14"/>
       <c r="K16" s="14"/>
       <c r="L16" s="14"/>
-      <c r="M16" s="15"/>
-      <c r="N16" s="15"/>
+      <c r="M16" s="14"/>
+      <c r="N16" s="14"/>
       <c r="O16" s="14"/>
-      <c r="P16" s="15"/>
-      <c r="Q16" s="15"/>
-      <c r="R16" s="15"/>
+      <c r="P16" s="14"/>
+      <c r="Q16" s="14"/>
+      <c r="R16" s="14"/>
       <c r="S16" s="14"/>
-      <c r="T16" s="15"/>
-      <c r="U16" s="15"/>
-      <c r="W16" s="41"/>
-      <c r="X16" s="42"/>
-      <c r="Y16" s="42"/>
-      <c r="Z16" s="42"/>
-      <c r="AA16" s="16" t="s">
+      <c r="T16" s="14"/>
+      <c r="U16" s="14"/>
+      <c r="W16" s="39"/>
+      <c r="X16" s="40"/>
+      <c r="Y16" s="40"/>
+      <c r="Z16" s="40"/>
+      <c r="AA16" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="AB16" s="17" t="b">
+      <c r="AB16" s="16" t="b">
         <f t="shared" ref="AB16" si="7">IF(X15&lt;=Z15,TRUE,FALSE)</f>
         <v>1</v>
       </c>
@@ -2450,37 +2541,37 @@
       <c r="C17" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="D17" s="15"/>
-      <c r="E17" s="15"/>
-      <c r="F17" s="15"/>
+      <c r="D17" s="14"/>
+      <c r="E17" s="14"/>
+      <c r="F17" s="14"/>
       <c r="G17" s="14"/>
-      <c r="H17" s="15"/>
-      <c r="I17" s="15"/>
-      <c r="J17" s="15"/>
+      <c r="H17" s="14"/>
+      <c r="I17" s="14"/>
+      <c r="J17" s="14"/>
       <c r="K17" s="14"/>
       <c r="L17" s="14"/>
-      <c r="M17" s="15"/>
+      <c r="M17" s="14"/>
       <c r="N17" s="14"/>
       <c r="O17" s="14"/>
-      <c r="P17" s="15"/>
-      <c r="Q17" s="15"/>
-      <c r="R17" s="15"/>
+      <c r="P17" s="14"/>
+      <c r="Q17" s="14"/>
+      <c r="R17" s="14"/>
       <c r="S17" s="14"/>
-      <c r="T17" s="15"/>
-      <c r="U17" s="15"/>
-      <c r="W17" s="41" t="s">
+      <c r="T17" s="14"/>
+      <c r="U17" s="14"/>
+      <c r="W17" s="39" t="s">
         <v>55</v>
       </c>
-      <c r="X17" s="42">
+      <c r="X17" s="40">
         <f>W36+W37</f>
         <v>0</v>
       </c>
-      <c r="Y17" s="42"/>
-      <c r="Z17" s="42"/>
-      <c r="AA17" s="16" t="s">
+      <c r="Y17" s="40"/>
+      <c r="Z17" s="40"/>
+      <c r="AA17" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="AB17" s="17" t="b">
+      <c r="AB17" s="16" t="b">
         <f t="shared" ref="AB17" si="8">IF(X17&gt;=Y17,TRUE,FALSE)</f>
         <v>1</v>
       </c>
@@ -2492,32 +2583,32 @@
       <c r="C18" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="D18" s="15"/>
-      <c r="E18" s="15"/>
-      <c r="F18" s="15"/>
+      <c r="D18" s="14"/>
+      <c r="E18" s="14"/>
+      <c r="F18" s="14"/>
       <c r="G18" s="14"/>
-      <c r="H18" s="15"/>
-      <c r="I18" s="15"/>
-      <c r="J18" s="15"/>
+      <c r="H18" s="14"/>
+      <c r="I18" s="14"/>
+      <c r="J18" s="14"/>
       <c r="K18" s="14"/>
       <c r="L18" s="14"/>
-      <c r="M18" s="15"/>
+      <c r="M18" s="14"/>
       <c r="N18" s="14"/>
       <c r="O18" s="14"/>
-      <c r="P18" s="15"/>
-      <c r="Q18" s="15"/>
-      <c r="R18" s="15"/>
+      <c r="P18" s="14"/>
+      <c r="Q18" s="14"/>
+      <c r="R18" s="14"/>
       <c r="S18" s="14"/>
-      <c r="T18" s="15"/>
-      <c r="U18" s="15"/>
-      <c r="W18" s="41"/>
-      <c r="X18" s="42"/>
-      <c r="Y18" s="42"/>
-      <c r="Z18" s="42"/>
-      <c r="AA18" s="16" t="s">
+      <c r="T18" s="14"/>
+      <c r="U18" s="14"/>
+      <c r="W18" s="39"/>
+      <c r="X18" s="40"/>
+      <c r="Y18" s="40"/>
+      <c r="Z18" s="40"/>
+      <c r="AA18" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="AB18" s="17" t="b">
+      <c r="AB18" s="16" t="b">
         <f t="shared" ref="AB18" si="9">IF(X17&lt;=Z17,TRUE,FALSE)</f>
         <v>1</v>
       </c>
@@ -2525,72 +2616,72 @@
     <row r="19" spans="2:31" x14ac:dyDescent="0.25">
       <c r="W19" s="4"/>
       <c r="X19" s="4"/>
-      <c r="Y19" s="31"/>
-      <c r="Z19" s="31"/>
+      <c r="Y19" s="29"/>
+      <c r="Z19" s="29"/>
     </row>
     <row r="20" spans="2:31" x14ac:dyDescent="0.25">
-      <c r="C20" s="18" t="s">
+      <c r="C20" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="D20" s="19"/>
-      <c r="E20" s="19"/>
-      <c r="F20" s="19"/>
-      <c r="G20" s="19"/>
-      <c r="H20" s="19"/>
-      <c r="I20" s="19"/>
-      <c r="J20" s="19"/>
-      <c r="K20" s="19"/>
-      <c r="L20" s="19"/>
-      <c r="M20" s="19"/>
-      <c r="N20" s="19"/>
-      <c r="O20" s="19"/>
-      <c r="P20" s="19"/>
-      <c r="Q20" s="19"/>
-      <c r="R20" s="19"/>
-      <c r="S20" s="19"/>
-      <c r="T20" s="19"/>
-      <c r="U20" s="19"/>
-      <c r="V20" s="20">
+      <c r="D20" s="18"/>
+      <c r="E20" s="18"/>
+      <c r="F20" s="18"/>
+      <c r="G20" s="18"/>
+      <c r="H20" s="18"/>
+      <c r="I20" s="18"/>
+      <c r="J20" s="18"/>
+      <c r="K20" s="18"/>
+      <c r="L20" s="18"/>
+      <c r="M20" s="18"/>
+      <c r="N20" s="18"/>
+      <c r="O20" s="18"/>
+      <c r="P20" s="18"/>
+      <c r="Q20" s="18"/>
+      <c r="R20" s="18"/>
+      <c r="S20" s="18"/>
+      <c r="T20" s="18"/>
+      <c r="U20" s="18"/>
+      <c r="V20" s="19">
         <f>SUM(D20:U20)</f>
         <v>0</v>
       </c>
-      <c r="X20" s="21">
+      <c r="X20" s="20">
         <f>SUM(X7:X17)</f>
         <v>0</v>
       </c>
-      <c r="Y20" s="21">
+      <c r="Y20" s="20">
         <f t="shared" ref="Y20:Z20" si="10">SUM(Y7:Y17)</f>
         <v>0</v>
       </c>
-      <c r="Z20" s="21">
+      <c r="Z20" s="20">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="2:31" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="C22" s="40" t="s">
+      <c r="C22" s="41" t="s">
         <v>59</v>
       </c>
-      <c r="D22" s="40"/>
-      <c r="E22" s="40"/>
-      <c r="F22" s="40"/>
-      <c r="G22" s="40"/>
-      <c r="H22" s="40"/>
-      <c r="I22" s="40"/>
-      <c r="J22" s="40"/>
-      <c r="K22" s="40"/>
-      <c r="L22" s="40"/>
-      <c r="M22" s="40"/>
-      <c r="N22" s="40"/>
-      <c r="O22" s="40"/>
-      <c r="P22" s="40"/>
-      <c r="Q22" s="40"/>
-      <c r="R22" s="40"/>
-      <c r="S22" s="40"/>
-      <c r="T22" s="40"/>
-      <c r="U22" s="40"/>
-      <c r="Y22" s="31"/>
-      <c r="Z22" s="31"/>
+      <c r="D22" s="41"/>
+      <c r="E22" s="41"/>
+      <c r="F22" s="41"/>
+      <c r="G22" s="41"/>
+      <c r="H22" s="41"/>
+      <c r="I22" s="41"/>
+      <c r="J22" s="41"/>
+      <c r="K22" s="41"/>
+      <c r="L22" s="41"/>
+      <c r="M22" s="41"/>
+      <c r="N22" s="41"/>
+      <c r="O22" s="41"/>
+      <c r="P22" s="41"/>
+      <c r="Q22" s="41"/>
+      <c r="R22" s="41"/>
+      <c r="S22" s="41"/>
+      <c r="T22" s="41"/>
+      <c r="U22" s="41"/>
+      <c r="Y22" s="29"/>
+      <c r="Z22" s="29"/>
     </row>
     <row r="23" spans="2:31" ht="18.75" x14ac:dyDescent="0.3">
       <c r="D23" s="5">
@@ -2647,12 +2738,12 @@
       <c r="U23" s="5">
         <v>18</v>
       </c>
-      <c r="AA23" s="22"/>
-      <c r="AB23" s="22" t="s">
+      <c r="AA23" s="21"/>
+      <c r="AB23" s="21" t="s">
         <v>60</v>
       </c>
-      <c r="AC23" s="22"/>
-      <c r="AD23" s="22"/>
+      <c r="AC23" s="21"/>
+      <c r="AD23" s="21"/>
     </row>
     <row r="24" spans="2:31" ht="30" x14ac:dyDescent="0.25">
       <c r="C24" s="6" t="s">
@@ -2712,20 +2803,20 @@
       <c r="U24" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="W24" s="23" t="s">
+      <c r="W24" s="22" t="s">
         <v>61</v>
       </c>
-      <c r="X24" s="23" t="s">
+      <c r="X24" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="Y24" s="49" t="s">
+      <c r="Y24" s="42" t="s">
         <v>67</v>
       </c>
-      <c r="Z24" s="50"/>
-      <c r="AB24" s="24" t="s">
+      <c r="Z24" s="43"/>
+      <c r="AB24" s="23" t="s">
         <v>63</v>
       </c>
-      <c r="AC24" s="25">
+      <c r="AC24" s="24">
         <f>SUMPRODUCT(D7:U18, D26:U37)</f>
         <v>0</v>
       </c>
@@ -2763,41 +2854,41 @@
       <c r="C26" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="D26" s="26"/>
-      <c r="E26" s="26"/>
-      <c r="F26" s="26"/>
-      <c r="G26" s="26"/>
-      <c r="H26" s="26"/>
-      <c r="I26" s="26"/>
-      <c r="J26" s="27"/>
-      <c r="K26" s="26"/>
-      <c r="L26" s="27"/>
-      <c r="M26" s="26"/>
-      <c r="N26" s="26"/>
-      <c r="O26" s="27"/>
-      <c r="P26" s="27"/>
-      <c r="Q26" s="26"/>
-      <c r="R26" s="27"/>
-      <c r="S26" s="26"/>
-      <c r="T26" s="26"/>
-      <c r="U26" s="26"/>
-      <c r="W26" s="28">
+      <c r="D26" s="25"/>
+      <c r="E26" s="25"/>
+      <c r="F26" s="25"/>
+      <c r="G26" s="25"/>
+      <c r="H26" s="25"/>
+      <c r="I26" s="25"/>
+      <c r="J26" s="25"/>
+      <c r="K26" s="25"/>
+      <c r="L26" s="25"/>
+      <c r="M26" s="25"/>
+      <c r="N26" s="25"/>
+      <c r="O26" s="25"/>
+      <c r="P26" s="25"/>
+      <c r="Q26" s="25"/>
+      <c r="R26" s="25"/>
+      <c r="S26" s="25"/>
+      <c r="T26" s="25"/>
+      <c r="U26" s="25"/>
+      <c r="W26" s="26">
         <f t="shared" ref="W26:W37" si="11">SUM(D26:U26)</f>
         <v>0</v>
       </c>
-      <c r="X26" s="43">
+      <c r="X26" s="30">
         <f>SUM(W26:W27)</f>
         <v>0</v>
       </c>
-      <c r="Y26" s="45">
+      <c r="Y26" s="32">
         <f>SUMPRODUCT(D7:U7, D26:U26)</f>
         <v>0</v>
       </c>
-      <c r="Z26" s="46"/>
-      <c r="AB26" s="34" t="s">
+      <c r="Z26" s="33"/>
+      <c r="AB26" s="46" t="s">
         <v>65</v>
       </c>
-      <c r="AC26" s="32"/>
+      <c r="AC26" s="44"/>
       <c r="AE26" s="1"/>
     </row>
     <row r="27" spans="2:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2807,36 +2898,36 @@
       <c r="C27" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="D27" s="26"/>
-      <c r="E27" s="26"/>
-      <c r="F27" s="26"/>
-      <c r="G27" s="26"/>
-      <c r="H27" s="26"/>
-      <c r="I27" s="26"/>
-      <c r="J27" s="27"/>
-      <c r="K27" s="26"/>
-      <c r="L27" s="27"/>
-      <c r="M27" s="26"/>
-      <c r="N27" s="26"/>
-      <c r="O27" s="27"/>
-      <c r="P27" s="27"/>
-      <c r="Q27" s="26"/>
-      <c r="R27" s="27"/>
-      <c r="S27" s="26"/>
-      <c r="T27" s="26"/>
-      <c r="U27" s="26"/>
-      <c r="W27" s="29">
+      <c r="D27" s="25"/>
+      <c r="E27" s="25"/>
+      <c r="F27" s="25"/>
+      <c r="G27" s="25"/>
+      <c r="H27" s="25"/>
+      <c r="I27" s="25"/>
+      <c r="J27" s="25"/>
+      <c r="K27" s="25"/>
+      <c r="L27" s="25"/>
+      <c r="M27" s="25"/>
+      <c r="N27" s="25"/>
+      <c r="O27" s="25"/>
+      <c r="P27" s="25"/>
+      <c r="Q27" s="25"/>
+      <c r="R27" s="25"/>
+      <c r="S27" s="25"/>
+      <c r="T27" s="25"/>
+      <c r="U27" s="25"/>
+      <c r="W27" s="27">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="X27" s="44"/>
-      <c r="Y27" s="47">
+      <c r="X27" s="31"/>
+      <c r="Y27" s="34">
         <f>SUMPRODUCT(D8:U8, D27:U27)</f>
         <v>0</v>
       </c>
-      <c r="Z27" s="48"/>
-      <c r="AB27" s="35"/>
-      <c r="AC27" s="33"/>
+      <c r="Z27" s="35"/>
+      <c r="AB27" s="47"/>
+      <c r="AC27" s="45"/>
       <c r="AE27" s="1"/>
     </row>
     <row r="28" spans="2:31" x14ac:dyDescent="0.25">
@@ -2846,37 +2937,37 @@
       <c r="C28" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="D28" s="26"/>
-      <c r="E28" s="26"/>
-      <c r="F28" s="26"/>
-      <c r="G28" s="26"/>
-      <c r="H28" s="26"/>
-      <c r="I28" s="26"/>
-      <c r="J28" s="26"/>
-      <c r="K28" s="26"/>
-      <c r="L28" s="26"/>
-      <c r="M28" s="26"/>
-      <c r="N28" s="26"/>
-      <c r="O28" s="26"/>
-      <c r="P28" s="26"/>
-      <c r="Q28" s="26"/>
-      <c r="R28" s="26"/>
-      <c r="S28" s="26"/>
-      <c r="T28" s="26"/>
-      <c r="U28" s="27"/>
-      <c r="W28" s="28">
+      <c r="D28" s="25"/>
+      <c r="E28" s="25"/>
+      <c r="F28" s="25"/>
+      <c r="G28" s="25"/>
+      <c r="H28" s="25"/>
+      <c r="I28" s="25"/>
+      <c r="J28" s="25"/>
+      <c r="K28" s="25"/>
+      <c r="L28" s="25"/>
+      <c r="M28" s="25"/>
+      <c r="N28" s="25"/>
+      <c r="O28" s="25"/>
+      <c r="P28" s="25"/>
+      <c r="Q28" s="25"/>
+      <c r="R28" s="25"/>
+      <c r="S28" s="25"/>
+      <c r="T28" s="25"/>
+      <c r="U28" s="25"/>
+      <c r="W28" s="26">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="X28" s="43">
+      <c r="X28" s="30">
         <f t="shared" ref="X28" si="12">SUM(W28:W29)</f>
         <v>0</v>
       </c>
-      <c r="Y28" s="45">
+      <c r="Y28" s="32">
         <f t="shared" ref="Y28:Y37" si="13">SUMPRODUCT(D9:U9, D28:U28)</f>
         <v>0</v>
       </c>
-      <c r="Z28" s="46"/>
+      <c r="Z28" s="33"/>
       <c r="AC28" s="1"/>
       <c r="AE28" s="1"/>
     </row>
@@ -2887,42 +2978,42 @@
       <c r="C29" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="D29" s="26"/>
-      <c r="E29" s="26"/>
-      <c r="F29" s="26"/>
-      <c r="G29" s="26"/>
-      <c r="H29" s="26"/>
-      <c r="I29" s="26"/>
-      <c r="J29" s="26"/>
-      <c r="K29" s="26"/>
-      <c r="L29" s="26"/>
-      <c r="M29" s="26"/>
-      <c r="N29" s="26"/>
-      <c r="O29" s="26"/>
-      <c r="P29" s="26"/>
-      <c r="Q29" s="26"/>
-      <c r="R29" s="26"/>
-      <c r="S29" s="26"/>
-      <c r="T29" s="26"/>
-      <c r="U29" s="27"/>
-      <c r="W29" s="29">
+      <c r="D29" s="25"/>
+      <c r="E29" s="25"/>
+      <c r="F29" s="25"/>
+      <c r="G29" s="25"/>
+      <c r="H29" s="25"/>
+      <c r="I29" s="25"/>
+      <c r="J29" s="25"/>
+      <c r="K29" s="25"/>
+      <c r="L29" s="25"/>
+      <c r="M29" s="25"/>
+      <c r="N29" s="25"/>
+      <c r="O29" s="25"/>
+      <c r="P29" s="25"/>
+      <c r="Q29" s="25"/>
+      <c r="R29" s="25"/>
+      <c r="S29" s="25"/>
+      <c r="T29" s="25"/>
+      <c r="U29" s="25"/>
+      <c r="W29" s="27">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="X29" s="44"/>
-      <c r="Y29" s="47">
+      <c r="X29" s="31"/>
+      <c r="Y29" s="34">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="Z29" s="48"/>
-      <c r="AB29" s="34" t="s">
+      <c r="Z29" s="35"/>
+      <c r="AB29" s="46" t="s">
         <v>66</v>
       </c>
-      <c r="AC29" s="36">
+      <c r="AC29" s="48">
         <f>AC24*AC26</f>
         <v>0</v>
       </c>
-      <c r="AD29" s="37"/>
+      <c r="AD29" s="49"/>
       <c r="AE29" s="1"/>
     </row>
     <row r="30" spans="2:31" x14ac:dyDescent="0.25">
@@ -2932,40 +3023,40 @@
       <c r="C30" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="D30" s="26"/>
-      <c r="E30" s="26"/>
-      <c r="F30" s="26"/>
-      <c r="G30" s="26"/>
-      <c r="H30" s="26"/>
-      <c r="I30" s="26"/>
-      <c r="J30" s="26"/>
-      <c r="K30" s="26"/>
-      <c r="L30" s="26"/>
-      <c r="M30" s="26"/>
-      <c r="N30" s="26"/>
-      <c r="O30" s="26"/>
-      <c r="P30" s="26"/>
-      <c r="Q30" s="26"/>
-      <c r="R30" s="26"/>
-      <c r="S30" s="26"/>
-      <c r="T30" s="26"/>
-      <c r="U30" s="27"/>
-      <c r="W30" s="28">
+      <c r="D30" s="25"/>
+      <c r="E30" s="25"/>
+      <c r="F30" s="25"/>
+      <c r="G30" s="25"/>
+      <c r="H30" s="25"/>
+      <c r="I30" s="25"/>
+      <c r="J30" s="25"/>
+      <c r="K30" s="25"/>
+      <c r="L30" s="25"/>
+      <c r="M30" s="25"/>
+      <c r="N30" s="25"/>
+      <c r="O30" s="25"/>
+      <c r="P30" s="25"/>
+      <c r="Q30" s="25"/>
+      <c r="R30" s="25"/>
+      <c r="S30" s="25"/>
+      <c r="T30" s="25"/>
+      <c r="U30" s="25"/>
+      <c r="W30" s="26">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="X30" s="43">
+      <c r="X30" s="30">
         <f t="shared" ref="X30" si="14">SUM(W30:W31)</f>
         <v>0</v>
       </c>
-      <c r="Y30" s="45">
+      <c r="Y30" s="32">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="Z30" s="46"/>
-      <c r="AB30" s="35"/>
-      <c r="AC30" s="38"/>
-      <c r="AD30" s="39"/>
+      <c r="Z30" s="33"/>
+      <c r="AB30" s="47"/>
+      <c r="AC30" s="50"/>
+      <c r="AD30" s="51"/>
       <c r="AE30" s="1"/>
     </row>
     <row r="31" spans="2:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2975,34 +3066,34 @@
       <c r="C31" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="D31" s="26"/>
-      <c r="E31" s="26"/>
-      <c r="F31" s="26"/>
-      <c r="G31" s="26"/>
-      <c r="H31" s="26"/>
-      <c r="I31" s="26"/>
-      <c r="J31" s="26"/>
-      <c r="K31" s="26"/>
-      <c r="L31" s="26"/>
-      <c r="M31" s="26"/>
-      <c r="N31" s="26"/>
-      <c r="O31" s="26"/>
-      <c r="P31" s="26"/>
-      <c r="Q31" s="26"/>
-      <c r="R31" s="26"/>
-      <c r="S31" s="26"/>
-      <c r="T31" s="26"/>
-      <c r="U31" s="27"/>
-      <c r="W31" s="30">
+      <c r="D31" s="25"/>
+      <c r="E31" s="25"/>
+      <c r="F31" s="25"/>
+      <c r="G31" s="25"/>
+      <c r="H31" s="25"/>
+      <c r="I31" s="25"/>
+      <c r="J31" s="25"/>
+      <c r="K31" s="25"/>
+      <c r="L31" s="25"/>
+      <c r="M31" s="25"/>
+      <c r="N31" s="25"/>
+      <c r="O31" s="25"/>
+      <c r="P31" s="25"/>
+      <c r="Q31" s="25"/>
+      <c r="R31" s="25"/>
+      <c r="S31" s="25"/>
+      <c r="T31" s="25"/>
+      <c r="U31" s="25"/>
+      <c r="W31" s="28">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="X31" s="51"/>
-      <c r="Y31" s="47">
+      <c r="X31" s="38"/>
+      <c r="Y31" s="34">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="Z31" s="48"/>
+      <c r="Z31" s="35"/>
       <c r="AC31" s="1"/>
       <c r="AE31" s="1"/>
     </row>
@@ -3013,37 +3104,37 @@
       <c r="C32" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="D32" s="27"/>
-      <c r="E32" s="27"/>
-      <c r="F32" s="27"/>
-      <c r="G32" s="26"/>
-      <c r="H32" s="27"/>
-      <c r="I32" s="27"/>
-      <c r="J32" s="27"/>
-      <c r="K32" s="27"/>
-      <c r="L32" s="27"/>
-      <c r="M32" s="27"/>
-      <c r="N32" s="27"/>
-      <c r="O32" s="26"/>
-      <c r="P32" s="27"/>
-      <c r="Q32" s="27"/>
-      <c r="R32" s="27"/>
-      <c r="S32" s="26"/>
-      <c r="T32" s="27"/>
-      <c r="U32" s="27"/>
-      <c r="W32" s="28">
+      <c r="D32" s="25"/>
+      <c r="E32" s="25"/>
+      <c r="F32" s="25"/>
+      <c r="G32" s="25"/>
+      <c r="H32" s="25"/>
+      <c r="I32" s="25"/>
+      <c r="J32" s="25"/>
+      <c r="K32" s="25"/>
+      <c r="L32" s="25"/>
+      <c r="M32" s="25"/>
+      <c r="N32" s="25"/>
+      <c r="O32" s="25"/>
+      <c r="P32" s="25"/>
+      <c r="Q32" s="25"/>
+      <c r="R32" s="25"/>
+      <c r="S32" s="25"/>
+      <c r="T32" s="25"/>
+      <c r="U32" s="25"/>
+      <c r="W32" s="26">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="X32" s="43">
+      <c r="X32" s="30">
         <f t="shared" ref="X32" si="15">SUM(W32:W33)</f>
         <v>0</v>
       </c>
-      <c r="Y32" s="45">
+      <c r="Y32" s="32">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="Z32" s="46"/>
+      <c r="Z32" s="33"/>
       <c r="AC32" s="1"/>
       <c r="AE32" s="1"/>
     </row>
@@ -3054,34 +3145,34 @@
       <c r="C33" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="D33" s="27"/>
-      <c r="E33" s="27"/>
-      <c r="F33" s="27"/>
-      <c r="G33" s="26"/>
-      <c r="H33" s="27"/>
-      <c r="I33" s="27"/>
-      <c r="J33" s="27"/>
-      <c r="K33" s="27"/>
-      <c r="L33" s="27"/>
-      <c r="M33" s="27"/>
-      <c r="N33" s="27"/>
-      <c r="O33" s="26"/>
-      <c r="P33" s="27"/>
-      <c r="Q33" s="27"/>
-      <c r="R33" s="27"/>
-      <c r="S33" s="26"/>
-      <c r="T33" s="27"/>
-      <c r="U33" s="27"/>
-      <c r="W33" s="29">
+      <c r="D33" s="25"/>
+      <c r="E33" s="25"/>
+      <c r="F33" s="25"/>
+      <c r="G33" s="25"/>
+      <c r="H33" s="25"/>
+      <c r="I33" s="25"/>
+      <c r="J33" s="25"/>
+      <c r="K33" s="25"/>
+      <c r="L33" s="25"/>
+      <c r="M33" s="25"/>
+      <c r="N33" s="25"/>
+      <c r="O33" s="25"/>
+      <c r="P33" s="25"/>
+      <c r="Q33" s="25"/>
+      <c r="R33" s="25"/>
+      <c r="S33" s="25"/>
+      <c r="T33" s="25"/>
+      <c r="U33" s="25"/>
+      <c r="W33" s="27">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="X33" s="44"/>
-      <c r="Y33" s="47">
+      <c r="X33" s="31"/>
+      <c r="Y33" s="34">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="Z33" s="48"/>
+      <c r="Z33" s="35"/>
       <c r="AC33" s="1"/>
       <c r="AE33" s="1"/>
     </row>
@@ -3092,37 +3183,37 @@
       <c r="C34" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="D34" s="27"/>
-      <c r="E34" s="27"/>
-      <c r="F34" s="27"/>
-      <c r="G34" s="26"/>
-      <c r="H34" s="27"/>
-      <c r="I34" s="27"/>
-      <c r="J34" s="27"/>
-      <c r="K34" s="26"/>
-      <c r="L34" s="26"/>
-      <c r="M34" s="27"/>
-      <c r="N34" s="27"/>
-      <c r="O34" s="26"/>
-      <c r="P34" s="27"/>
-      <c r="Q34" s="27"/>
-      <c r="R34" s="27"/>
-      <c r="S34" s="26"/>
-      <c r="T34" s="27"/>
-      <c r="U34" s="27"/>
-      <c r="W34" s="28">
+      <c r="D34" s="25"/>
+      <c r="E34" s="25"/>
+      <c r="F34" s="25"/>
+      <c r="G34" s="25"/>
+      <c r="H34" s="25"/>
+      <c r="I34" s="25"/>
+      <c r="J34" s="25"/>
+      <c r="K34" s="25"/>
+      <c r="L34" s="25"/>
+      <c r="M34" s="25"/>
+      <c r="N34" s="25"/>
+      <c r="O34" s="25"/>
+      <c r="P34" s="25"/>
+      <c r="Q34" s="25"/>
+      <c r="R34" s="25"/>
+      <c r="S34" s="25"/>
+      <c r="T34" s="25"/>
+      <c r="U34" s="25"/>
+      <c r="W34" s="26">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="X34" s="43">
+      <c r="X34" s="30">
         <f t="shared" ref="X34" si="16">SUM(W34:W35)</f>
         <v>0</v>
       </c>
-      <c r="Y34" s="45">
+      <c r="Y34" s="32">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="Z34" s="46"/>
+      <c r="Z34" s="33"/>
       <c r="AC34" s="1"/>
       <c r="AE34" s="1"/>
     </row>
@@ -3133,34 +3224,34 @@
       <c r="C35" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="D35" s="27"/>
-      <c r="E35" s="27"/>
-      <c r="F35" s="27"/>
-      <c r="G35" s="26"/>
-      <c r="H35" s="27"/>
-      <c r="I35" s="27"/>
-      <c r="J35" s="27"/>
-      <c r="K35" s="26"/>
-      <c r="L35" s="26"/>
-      <c r="M35" s="27"/>
-      <c r="N35" s="27"/>
-      <c r="O35" s="26"/>
-      <c r="P35" s="27"/>
-      <c r="Q35" s="27"/>
-      <c r="R35" s="27"/>
-      <c r="S35" s="26"/>
-      <c r="T35" s="27"/>
-      <c r="U35" s="27"/>
-      <c r="W35" s="29">
+      <c r="D35" s="25"/>
+      <c r="E35" s="25"/>
+      <c r="F35" s="25"/>
+      <c r="G35" s="25"/>
+      <c r="H35" s="25"/>
+      <c r="I35" s="25"/>
+      <c r="J35" s="25"/>
+      <c r="K35" s="25"/>
+      <c r="L35" s="25"/>
+      <c r="M35" s="25"/>
+      <c r="N35" s="25"/>
+      <c r="O35" s="25"/>
+      <c r="P35" s="25"/>
+      <c r="Q35" s="25"/>
+      <c r="R35" s="25"/>
+      <c r="S35" s="25"/>
+      <c r="T35" s="25"/>
+      <c r="U35" s="25"/>
+      <c r="W35" s="27">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="X35" s="44"/>
-      <c r="Y35" s="47">
+      <c r="X35" s="31"/>
+      <c r="Y35" s="34">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="Z35" s="48"/>
+      <c r="Z35" s="35"/>
       <c r="AC35" s="1"/>
       <c r="AE35" s="1"/>
     </row>
@@ -3171,37 +3262,37 @@
       <c r="C36" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="D36" s="27"/>
-      <c r="E36" s="27"/>
-      <c r="F36" s="27"/>
-      <c r="G36" s="26"/>
-      <c r="H36" s="27"/>
-      <c r="I36" s="27"/>
-      <c r="J36" s="27"/>
-      <c r="K36" s="26"/>
-      <c r="L36" s="26"/>
-      <c r="M36" s="27"/>
-      <c r="N36" s="26"/>
-      <c r="O36" s="26"/>
-      <c r="P36" s="27"/>
-      <c r="Q36" s="27"/>
-      <c r="R36" s="27"/>
-      <c r="S36" s="26"/>
-      <c r="T36" s="27"/>
-      <c r="U36" s="27"/>
-      <c r="W36" s="28">
+      <c r="D36" s="25"/>
+      <c r="E36" s="25"/>
+      <c r="F36" s="25"/>
+      <c r="G36" s="25"/>
+      <c r="H36" s="25"/>
+      <c r="I36" s="25"/>
+      <c r="J36" s="25"/>
+      <c r="K36" s="25"/>
+      <c r="L36" s="25"/>
+      <c r="M36" s="25"/>
+      <c r="N36" s="25"/>
+      <c r="O36" s="25"/>
+      <c r="P36" s="25"/>
+      <c r="Q36" s="25"/>
+      <c r="R36" s="25"/>
+      <c r="S36" s="25"/>
+      <c r="T36" s="25"/>
+      <c r="U36" s="25"/>
+      <c r="W36" s="26">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="X36" s="43">
+      <c r="X36" s="30">
         <f t="shared" ref="X36" si="17">SUM(W36:W37)</f>
         <v>0</v>
       </c>
-      <c r="Y36" s="45">
+      <c r="Y36" s="32">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="Z36" s="46"/>
+      <c r="Z36" s="33"/>
       <c r="AC36" s="1"/>
       <c r="AE36" s="1"/>
     </row>
@@ -3212,34 +3303,34 @@
       <c r="C37" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="D37" s="27"/>
-      <c r="E37" s="27"/>
-      <c r="F37" s="27"/>
-      <c r="G37" s="26"/>
-      <c r="H37" s="27"/>
-      <c r="I37" s="27"/>
-      <c r="J37" s="27"/>
-      <c r="K37" s="26"/>
-      <c r="L37" s="26"/>
-      <c r="M37" s="27"/>
-      <c r="N37" s="26"/>
-      <c r="O37" s="26"/>
-      <c r="P37" s="27"/>
-      <c r="Q37" s="27"/>
-      <c r="R37" s="27"/>
-      <c r="S37" s="26"/>
-      <c r="T37" s="27"/>
-      <c r="U37" s="27"/>
-      <c r="W37" s="29">
+      <c r="D37" s="25"/>
+      <c r="E37" s="25"/>
+      <c r="F37" s="25"/>
+      <c r="G37" s="25"/>
+      <c r="H37" s="25"/>
+      <c r="I37" s="25"/>
+      <c r="J37" s="25"/>
+      <c r="K37" s="25"/>
+      <c r="L37" s="25"/>
+      <c r="M37" s="25"/>
+      <c r="N37" s="25"/>
+      <c r="O37" s="25"/>
+      <c r="P37" s="25"/>
+      <c r="Q37" s="25"/>
+      <c r="R37" s="25"/>
+      <c r="S37" s="25"/>
+      <c r="T37" s="25"/>
+      <c r="U37" s="25"/>
+      <c r="W37" s="27">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="X37" s="44"/>
-      <c r="Y37" s="47">
+      <c r="X37" s="31"/>
+      <c r="Y37" s="34">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="Z37" s="48"/>
+      <c r="Z37" s="35"/>
       <c r="AC37" s="1"/>
       <c r="AE37" s="1"/>
     </row>
@@ -3249,94 +3340,94 @@
       <c r="AE38" s="1"/>
     </row>
     <row r="39" spans="2:31" x14ac:dyDescent="0.25">
-      <c r="C39" s="18" t="s">
+      <c r="C39" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="D39" s="19">
+      <c r="D39" s="18">
         <f>SUM(D26:D37)</f>
         <v>0</v>
       </c>
-      <c r="E39" s="19">
+      <c r="E39" s="18">
         <f t="shared" ref="E39:U39" si="18">SUM(E26:E37)</f>
         <v>0</v>
       </c>
-      <c r="F39" s="19">
+      <c r="F39" s="18">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="G39" s="19">
+      <c r="G39" s="18">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="H39" s="19">
+      <c r="H39" s="18">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="I39" s="19">
+      <c r="I39" s="18">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="J39" s="19">
+      <c r="J39" s="18">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="K39" s="19">
+      <c r="K39" s="18">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="L39" s="19">
+      <c r="L39" s="18">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="M39" s="19">
+      <c r="M39" s="18">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="N39" s="19">
+      <c r="N39" s="18">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="O39" s="19">
+      <c r="O39" s="18">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="P39" s="19">
+      <c r="P39" s="18">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="Q39" s="19">
+      <c r="Q39" s="18">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="R39" s="19">
+      <c r="R39" s="18">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="S39" s="19">
+      <c r="S39" s="18">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="T39" s="19">
+      <c r="T39" s="18">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="U39" s="19">
+      <c r="U39" s="18">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="V39" s="20">
+      <c r="V39" s="19">
         <f>SUM(D39:U39)</f>
         <v>0</v>
       </c>
-      <c r="X39" s="23">
+      <c r="X39" s="22">
         <f>SUM(X26:X37)</f>
         <v>0</v>
       </c>
-      <c r="Y39" s="52">
+      <c r="Y39" s="36">
         <f>SUM(Y26:Y37)</f>
         <v>0</v>
       </c>
-      <c r="Z39" s="52"/>
+      <c r="Z39" s="36"/>
       <c r="AC39" s="1"/>
       <c r="AE39" s="1"/>
     </row>
@@ -3345,91 +3436,91 @@
       <c r="AE40" s="1"/>
     </row>
     <row r="41" spans="2:31" x14ac:dyDescent="0.25">
-      <c r="D41" s="17" t="b">
+      <c r="D41" s="16" t="b">
         <f>IF(D20=D39,TRUE,FALSE)</f>
         <v>1</v>
       </c>
-      <c r="E41" s="17" t="b">
+      <c r="E41" s="16" t="b">
         <f t="shared" ref="E41:V41" si="19">IF(E20=E39,TRUE,FALSE)</f>
         <v>1</v>
       </c>
-      <c r="F41" s="17" t="b">
+      <c r="F41" s="16" t="b">
         <f t="shared" si="19"/>
         <v>1</v>
       </c>
-      <c r="G41" s="17" t="b">
+      <c r="G41" s="16" t="b">
         <f t="shared" si="19"/>
         <v>1</v>
       </c>
-      <c r="H41" s="17" t="b">
+      <c r="H41" s="16" t="b">
         <f t="shared" si="19"/>
         <v>1</v>
       </c>
-      <c r="I41" s="17" t="b">
+      <c r="I41" s="16" t="b">
         <f t="shared" si="19"/>
         <v>1</v>
       </c>
-      <c r="J41" s="17" t="b">
+      <c r="J41" s="16" t="b">
         <f t="shared" si="19"/>
         <v>1</v>
       </c>
-      <c r="K41" s="17" t="b">
+      <c r="K41" s="16" t="b">
         <f t="shared" si="19"/>
         <v>1</v>
       </c>
-      <c r="L41" s="17" t="b">
+      <c r="L41" s="16" t="b">
         <f t="shared" si="19"/>
         <v>1</v>
       </c>
-      <c r="M41" s="17" t="b">
+      <c r="M41" s="16" t="b">
         <f t="shared" si="19"/>
         <v>1</v>
       </c>
-      <c r="N41" s="17" t="b">
+      <c r="N41" s="16" t="b">
         <f t="shared" si="19"/>
         <v>1</v>
       </c>
-      <c r="O41" s="17" t="b">
+      <c r="O41" s="16" t="b">
         <f t="shared" si="19"/>
         <v>1</v>
       </c>
-      <c r="P41" s="17" t="b">
+      <c r="P41" s="16" t="b">
         <f t="shared" si="19"/>
         <v>1</v>
       </c>
-      <c r="Q41" s="17" t="b">
+      <c r="Q41" s="16" t="b">
         <f t="shared" si="19"/>
         <v>1</v>
       </c>
-      <c r="R41" s="17" t="b">
+      <c r="R41" s="16" t="b">
         <f t="shared" si="19"/>
         <v>1</v>
       </c>
-      <c r="S41" s="17" t="b">
+      <c r="S41" s="16" t="b">
         <f t="shared" si="19"/>
         <v>1</v>
       </c>
-      <c r="T41" s="17" t="b">
+      <c r="T41" s="16" t="b">
         <f t="shared" si="19"/>
         <v>1</v>
       </c>
-      <c r="U41" s="17" t="b">
+      <c r="U41" s="16" t="b">
         <f t="shared" si="19"/>
         <v>1</v>
       </c>
-      <c r="V41" s="17" t="b">
+      <c r="V41" s="16" t="b">
         <f t="shared" si="19"/>
         <v>1</v>
       </c>
-      <c r="X41" s="17" t="b">
+      <c r="X41" s="16" t="b">
         <f>IF(X20=X39,TRUE,FALSE)</f>
         <v>1</v>
       </c>
-      <c r="Y41" s="53" t="b">
+      <c r="Y41" s="37" t="b">
         <f>IF(AC24=Y39,TRUE,FALSE)</f>
         <v>1</v>
       </c>
-      <c r="Z41" s="53"/>
+      <c r="Z41" s="37"/>
       <c r="AC41" s="1"/>
       <c r="AE41" s="1"/>
     </row>
@@ -3470,47 +3561,7 @@
       <c r="Z50" s="3"/>
     </row>
   </sheetData>
-  <protectedRanges>
-    <protectedRange sqref="D7:U18" name="CostMatrix"/>
-    <protectedRange sqref="D26:U37" name="DecisionVariables"/>
-  </protectedRanges>
   <mergeCells count="52">
-    <mergeCell ref="X36:X37"/>
-    <mergeCell ref="Y36:Z36"/>
-    <mergeCell ref="Y37:Z37"/>
-    <mergeCell ref="Y39:Z39"/>
-    <mergeCell ref="Y41:Z41"/>
-    <mergeCell ref="X32:X33"/>
-    <mergeCell ref="Y32:Z32"/>
-    <mergeCell ref="Y33:Z33"/>
-    <mergeCell ref="X34:X35"/>
-    <mergeCell ref="Y34:Z34"/>
-    <mergeCell ref="Y35:Z35"/>
-    <mergeCell ref="X28:X29"/>
-    <mergeCell ref="Y28:Z28"/>
-    <mergeCell ref="Y29:Z29"/>
-    <mergeCell ref="X30:X31"/>
-    <mergeCell ref="Y30:Z30"/>
-    <mergeCell ref="Y31:Z31"/>
-    <mergeCell ref="W17:W18"/>
-    <mergeCell ref="X17:X18"/>
-    <mergeCell ref="Y17:Y18"/>
-    <mergeCell ref="Z17:Z18"/>
-    <mergeCell ref="C22:U22"/>
-    <mergeCell ref="W13:W14"/>
-    <mergeCell ref="X13:X14"/>
-    <mergeCell ref="Y13:Y14"/>
-    <mergeCell ref="Z13:Z14"/>
-    <mergeCell ref="W15:W16"/>
-    <mergeCell ref="X15:X16"/>
-    <mergeCell ref="Y15:Y16"/>
-    <mergeCell ref="Z15:Z16"/>
-    <mergeCell ref="Y11:Y12"/>
-    <mergeCell ref="Z11:Z12"/>
-    <mergeCell ref="X26:X27"/>
-    <mergeCell ref="Y26:Z26"/>
-    <mergeCell ref="Y27:Z27"/>
-    <mergeCell ref="Y24:Z24"/>
     <mergeCell ref="AC26:AC27"/>
     <mergeCell ref="AB26:AB27"/>
     <mergeCell ref="AB29:AB30"/>
@@ -3527,38 +3578,77 @@
     <mergeCell ref="Z9:Z10"/>
     <mergeCell ref="W11:W12"/>
     <mergeCell ref="X11:X12"/>
+    <mergeCell ref="Y11:Y12"/>
+    <mergeCell ref="Z11:Z12"/>
+    <mergeCell ref="X26:X27"/>
+    <mergeCell ref="Y26:Z26"/>
+    <mergeCell ref="Y27:Z27"/>
+    <mergeCell ref="Y24:Z24"/>
+    <mergeCell ref="W13:W14"/>
+    <mergeCell ref="X13:X14"/>
+    <mergeCell ref="Y13:Y14"/>
+    <mergeCell ref="Z13:Z14"/>
+    <mergeCell ref="W15:W16"/>
+    <mergeCell ref="X15:X16"/>
+    <mergeCell ref="Y15:Y16"/>
+    <mergeCell ref="Z15:Z16"/>
+    <mergeCell ref="W17:W18"/>
+    <mergeCell ref="X17:X18"/>
+    <mergeCell ref="Y17:Y18"/>
+    <mergeCell ref="Z17:Z18"/>
+    <mergeCell ref="C22:U22"/>
+    <mergeCell ref="X28:X29"/>
+    <mergeCell ref="Y28:Z28"/>
+    <mergeCell ref="Y29:Z29"/>
+    <mergeCell ref="X30:X31"/>
+    <mergeCell ref="Y30:Z30"/>
+    <mergeCell ref="Y31:Z31"/>
+    <mergeCell ref="X32:X33"/>
+    <mergeCell ref="Y32:Z32"/>
+    <mergeCell ref="Y33:Z33"/>
+    <mergeCell ref="X34:X35"/>
+    <mergeCell ref="Y34:Z34"/>
+    <mergeCell ref="Y35:Z35"/>
+    <mergeCell ref="X36:X37"/>
+    <mergeCell ref="Y36:Z36"/>
+    <mergeCell ref="Y37:Z37"/>
+    <mergeCell ref="Y39:Z39"/>
+    <mergeCell ref="Y41:Z41"/>
   </mergeCells>
   <conditionalFormatting sqref="D7:U18">
-    <cfRule type="cellIs" dxfId="7" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
+      <formula>999</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
       <formula>999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D26:U37">
-    <cfRule type="cellIs" dxfId="6" priority="8" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="16" priority="9" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D41:V41">
-    <cfRule type="containsText" dxfId="5" priority="6" operator="containsText" text="TRUE">
+    <cfRule type="containsText" dxfId="15" priority="7" operator="containsText" text="TRUE">
       <formula>NOT(ISERROR(SEARCH("TRUE",D41)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="4" priority="7" operator="containsText" text="FALSE">
+    <cfRule type="containsText" dxfId="14" priority="8" operator="containsText" text="FALSE">
       <formula>NOT(ISERROR(SEARCH("FALSE",D41)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X41:Y41">
-    <cfRule type="containsText" dxfId="3" priority="2" operator="containsText" text="TRUE">
+    <cfRule type="containsText" dxfId="13" priority="3" operator="containsText" text="TRUE">
       <formula>NOT(ISERROR(SEARCH("TRUE",X41)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="FALSE">
+    <cfRule type="containsText" dxfId="12" priority="4" operator="containsText" text="FALSE">
       <formula>NOT(ISERROR(SEARCH("FALSE",X41)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB7:AB18">
-    <cfRule type="containsText" dxfId="1" priority="4" operator="containsText" text="TRUE">
+    <cfRule type="containsText" dxfId="11" priority="5" operator="containsText" text="TRUE">
       <formula>NOT(ISERROR(SEARCH("TRUE",AB7)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="5" operator="containsText" text="FALSE">
+    <cfRule type="containsText" dxfId="10" priority="6" operator="containsText" text="FALSE">
       <formula>NOT(ISERROR(SEARCH("FALSE",AB7)))</formula>
     </cfRule>
   </conditionalFormatting>
